--- a/results/tables/Pareto前沿解集.xlsx
+++ b/results/tables/Pareto前沿解集.xlsx
@@ -555,73 +555,73 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1627.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.9757714744741556</v>
       </c>
       <c r="D2" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>7.26432956248026e-08</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="M2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="U2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -629,25 +629,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>54.40000000000001</v>
+        <v>52.8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9777090099402329</v>
+        <v>0.997233024517562</v>
       </c>
       <c r="D3" t="n">
-        <v>7.818480260637344e-06</v>
+        <v>8.72980288141136e-08</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -659,37 +659,37 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -703,19 +703,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>84</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9996498857519347</v>
+        <v>0.9757714744741556</v>
       </c>
       <c r="D4" t="n">
-        <v>8.629214578856289e-06</v>
+        <v>7.26432956248026e-08</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -742,28 +742,28 @@
         <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -777,43 +777,43 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>60.8</v>
+        <v>300.4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9769874938774331</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>7.607721994180541e-06</v>
+        <v>1.183621452945349e-09</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
@@ -825,25 +825,25 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -851,43 +851,43 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>93.60000000000001</v>
+        <v>296.4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9884438424405779</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>7.266724376856037e-06</v>
+        <v>1.65888101154397e-09</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
@@ -899,25 +899,25 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -925,13 +925,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>105.6</v>
+        <v>205.6</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9917781942199666</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>7.100867741310708e-06</v>
+        <v>1.708130596477537e-09</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -943,55 +943,55 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>28</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>15</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>46</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>16</v>
       </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>25</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>15</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -999,13 +999,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9870452793839639</v>
+        <v>0.9933943811092961</v>
       </c>
       <c r="D8" t="n">
-        <v>7.537924321777452e-06</v>
+        <v>5.024189151858325e-08</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1017,37 +1017,37 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1059,13 +1059,13 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1073,13 +1073,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>320.4</v>
+        <v>43.2</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.9811969337161628</v>
       </c>
       <c r="D9" t="n">
-        <v>4.318572148438689e-06</v>
+        <v>7.194608099021132e-08</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1088,16 +1088,16 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1106,40 +1106,40 @@
         <v>15</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>8</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>6</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1147,25 +1147,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>108.8</v>
+        <v>48.8</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0.9930371507944292</v>
       </c>
       <c r="D10" t="n">
-        <v>8.239696867594876e-06</v>
+        <v>8.134310360734383e-08</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1186,31 +1186,31 @@
         <v>7</v>
       </c>
       <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>5</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>2</v>
@@ -1221,13 +1221,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>85.59999999999999</v>
+        <v>98.80000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9834969582372649</v>
+        <v>0.9983362808662395</v>
       </c>
       <c r="D11" t="n">
-        <v>7.25885809856751e-06</v>
+        <v>3.715039472609959e-08</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1239,13 +1239,13 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1257,31 +1257,31 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
@@ -1295,13 +1295,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1032</v>
+        <v>101.6</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0.9978708607215191</v>
       </c>
       <c r="D12" t="n">
-        <v>7.729940113693214e-07</v>
+        <v>2.955752501414561e-08</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1310,58 +1310,58 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>124</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>17</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
         <v>9</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>20</v>
-      </c>
-      <c r="N12" t="n">
-        <v>12</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
         <v>16</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>19</v>
-      </c>
-      <c r="R12" t="n">
-        <v>43</v>
-      </c>
-      <c r="S12" t="n">
-        <v>16</v>
-      </c>
-      <c r="T12" t="n">
-        <v>10</v>
-      </c>
       <c r="U12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
+        <v>23</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
         <v>3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>18</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1369,13 +1369,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>265.6</v>
+        <v>90</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0.9902230963278893</v>
       </c>
       <c r="D13" t="n">
-        <v>4.916297314410648e-06</v>
+        <v>2.70969701398583e-08</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1384,58 +1384,58 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>15</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>25</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>5</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
         <v>17</v>
       </c>
-      <c r="M13" t="n">
-        <v>6</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>6</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>9</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>7</v>
-      </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1443,13 +1443,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>56</v>
+        <v>164.4</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9786777776732716</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.814362186566776e-06</v>
+        <v>6.913907659487443e-09</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1461,13 +1461,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1479,37 +1479,37 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -1517,73 +1517,73 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>1331.6</v>
+        <v>123.2</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.869273522137085e-07</v>
+        <v>1.600138619241858e-08</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>136</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>22</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>15</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>29</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>10</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>22</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
         <v>24</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>13</v>
-      </c>
-      <c r="L15" t="n">
-        <v>15</v>
-      </c>
-      <c r="M15" t="n">
-        <v>27</v>
-      </c>
-      <c r="N15" t="n">
-        <v>10</v>
-      </c>
-      <c r="O15" t="n">
-        <v>15</v>
-      </c>
-      <c r="P15" t="n">
-        <v>71</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>24</v>
-      </c>
-      <c r="R15" t="n">
-        <v>20</v>
-      </c>
-      <c r="S15" t="n">
-        <v>21</v>
-      </c>
-      <c r="T15" t="n">
-        <v>9</v>
-      </c>
-      <c r="U15" t="n">
-        <v>23</v>
-      </c>
-      <c r="V15" t="n">
-        <v>45</v>
-      </c>
       <c r="W15" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1591,13 +1591,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>67.59999999999999</v>
+        <v>49.6</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9799039165505075</v>
+        <v>0.9837195333383197</v>
       </c>
       <c r="D16" t="n">
-        <v>7.464426118122873e-06</v>
+        <v>6.567652485531559e-08</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1612,10 +1612,10 @@
         <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1627,13 +1627,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1651,13 +1651,13 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1665,73 +1665,73 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>829.2</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0.9945314650016144</v>
       </c>
       <c r="D17" t="n">
-        <v>1.527873248338691e-06</v>
+        <v>6.02830539185563e-08</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
         <v>12</v>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>14</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -1739,13 +1739,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>60.8</v>
+        <v>44.8</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9844800400609668</v>
+        <v>0.9847312922412765</v>
       </c>
       <c r="D18" t="n">
-        <v>7.725209670329741e-06</v>
+        <v>7.643090342215271e-08</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1769,19 +1769,19 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>1160</v>
+        <v>59.2</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0.9952367285441565</v>
       </c>
       <c r="D19" t="n">
-        <v>5.990574053894157e-07</v>
+        <v>5.954104703800702e-08</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1828,58 +1828,58 @@
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="M19" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="U19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="W19" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -1887,13 +1887,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>389.2</v>
+        <v>44.8</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0.9794195326839883</v>
       </c>
       <c r="D20" t="n">
-        <v>3.754719322654549e-06</v>
+        <v>6.992205489469146e-08</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1902,58 +1902,58 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>15</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>5</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>15</v>
-      </c>
-      <c r="M20" t="n">
-        <v>10</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3</v>
-      </c>
-      <c r="O20" t="n">
-        <v>8</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1961,13 +1961,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>364.4</v>
+        <v>47.2</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9995767393646375</v>
+        <v>0.9850387065678776</v>
       </c>
       <c r="D21" t="n">
-        <v>4.17625246428546e-06</v>
+        <v>7.278299868573341e-08</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1976,58 +1976,58 @@
         <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>15</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>5</v>
       </c>
-      <c r="I21" t="n">
-        <v>10</v>
-      </c>
-      <c r="J21" t="n">
-        <v>28</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>15</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
         <v>8</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>8</v>
-      </c>
-      <c r="P21" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>7</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -2035,13 +2035,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>1256.4</v>
+        <v>161.2</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>4.047371057287857e-07</v>
+        <v>8.216727384572222e-09</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -2050,58 +2050,58 @@
         <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>139</v>
+        <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>37</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>32</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>35</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
         <v>22</v>
-      </c>
-      <c r="N22" t="n">
-        <v>51</v>
-      </c>
-      <c r="O22" t="n">
-        <v>17</v>
-      </c>
-      <c r="P22" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>23</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2</v>
-      </c>
-      <c r="S22" t="n">
-        <v>17</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>18</v>
-      </c>
-      <c r="V22" t="n">
-        <v>105</v>
-      </c>
-      <c r="W22" t="n">
-        <v>20</v>
-      </c>
-      <c r="X22" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -2109,13 +2109,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>437.6</v>
+        <v>86</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0.9900310604307805</v>
       </c>
       <c r="D23" t="n">
-        <v>3.568845380420556e-06</v>
+        <v>3.126955113980689e-08</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -2124,58 +2124,58 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>15</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>29</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
         <v>10</v>
       </c>
-      <c r="I23" t="n">
-        <v>12</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" t="n">
-        <v>9</v>
-      </c>
-      <c r="M23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>6</v>
-      </c>
-      <c r="P23" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>7</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
       <c r="U23" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="W23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2183,13 +2183,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>509.6</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0.9823413437820173</v>
       </c>
       <c r="D24" t="n">
-        <v>3.146105946451891e-06</v>
+        <v>6.832074451889226e-08</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -2198,58 +2198,58 @@
         <v>2</v>
       </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>15</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>8</v>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>14</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4</v>
-      </c>
-      <c r="L24" t="n">
-        <v>11</v>
-      </c>
-      <c r="M24" t="n">
-        <v>12</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
       <c r="O24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="U24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -2257,13 +2257,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>200</v>
+        <v>66.80000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>0.99645552964944</v>
+        <v>0.9879689218672889</v>
       </c>
       <c r="D25" t="n">
-        <v>5.701043114301624e-06</v>
+        <v>5.021170872908424e-08</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -2272,58 +2272,58 @@
         <v>2</v>
       </c>
       <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>11</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>15</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>11</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>15</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
         <v>4</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>15</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3</v>
-      </c>
-      <c r="O25" t="n">
-        <v>5</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>24</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>24</v>
-      </c>
-      <c r="U25" t="n">
-        <v>4</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2331,73 +2331,73 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>1448</v>
+        <v>43.2</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0.9769874938774331</v>
       </c>
       <c r="D26" t="n">
-        <v>1.694434879506493e-07</v>
+        <v>7.164940569285091e-08</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>144</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="M26" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="Q26" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="U26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -2405,13 +2405,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>379.6</v>
+        <v>104</v>
       </c>
       <c r="C27" t="n">
-        <v>0.998105369918045</v>
+        <v>0.9989058094488751</v>
       </c>
       <c r="D27" t="n">
-        <v>3.891140226936588e-06</v>
+        <v>2.614172041022563e-08</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -2420,58 +2420,58 @@
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>14</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>15</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>25</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
         <v>10</v>
       </c>
-      <c r="J27" t="n">
-        <v>5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>15</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
         <v>8</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>8</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>7</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W27" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2479,13 +2479,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>965.2</v>
+        <v>63.6</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0.9921848831031561</v>
       </c>
       <c r="D28" t="n">
-        <v>9.659339782866717e-07</v>
+        <v>5.351702081668719e-08</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -2494,58 +2494,58 @@
         <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>15</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>13</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
         <v>8</v>
       </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>20</v>
-      </c>
-      <c r="N28" t="n">
-        <v>31</v>
-      </c>
-      <c r="O28" t="n">
-        <v>16</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>16</v>
-      </c>
-      <c r="R28" t="n">
-        <v>45</v>
-      </c>
-      <c r="S28" t="n">
-        <v>16</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>18</v>
-      </c>
-      <c r="V28" t="n">
-        <v>13</v>
-      </c>
       <c r="W28" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2553,13 +2553,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>75.59999999999999</v>
+        <v>56</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9897713686148372</v>
+        <v>0.9829260172104262</v>
       </c>
       <c r="D29" t="n">
-        <v>7.435143629835728e-06</v>
+        <v>5.547424396635796e-08</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2571,13 +2571,13 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2586,22 +2586,22 @@
         <v>15</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
         <v>6</v>
       </c>
       <c r="O29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -2610,16 +2610,16 @@
         <v>6</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -2627,13 +2627,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>546.4</v>
+        <v>191.2</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>2.998094680810297e-06</v>
+        <v>3.920201700590394e-09</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2642,58 +2642,58 @@
         <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="I30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
+        <v>15</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>39</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>16</v>
       </c>
-      <c r="M30" t="n">
-        <v>10</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="n">
-        <v>11</v>
-      </c>
-      <c r="P30" t="n">
-        <v>3</v>
-      </c>
       <c r="Q30" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="U30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="W30" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31">
@@ -2701,13 +2701,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>112</v>
+        <v>70.80000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9930484811159127</v>
+        <v>0.9909210124406265</v>
       </c>
       <c r="D31" t="n">
-        <v>7.09246530856327e-06</v>
+        <v>4.563478570682803e-08</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -2719,44 +2719,44 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
+        <v>5</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
         <v>9</v>
       </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>6</v>
-      </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
@@ -2764,10 +2764,10 @@
         <v>7</v>
       </c>
       <c r="W31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2775,13 +2775,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>95.2</v>
+        <v>43.2</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9938866693427035</v>
+        <v>0.9791400955495581</v>
       </c>
       <c r="D32" t="n">
-        <v>7.231665240420453e-06</v>
+        <v>7.184082407812808e-08</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -2793,13 +2793,13 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2814,16 +2814,16 @@
         <v>7</v>
       </c>
       <c r="O32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -2832,10 +2832,10 @@
         <v>6</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -2849,13 +2849,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>308.8</v>
+        <v>137.6</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>4.748191281477033e-06</v>
+        <v>1.299551262335245e-08</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -2864,37 +2864,37 @@
         <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="O33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>8</v>
@@ -2903,16 +2903,16 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="W33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -2923,13 +2923,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>618</v>
+        <v>78</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0.9925937587925283</v>
       </c>
       <c r="D34" t="n">
-        <v>2.51357702284186e-06</v>
+        <v>4.034386388251058e-08</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -2938,58 +2938,58 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I34" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M34" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O34" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" t="n">
-        <v>12</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
       <c r="U34" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2997,13 +2997,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>554</v>
+        <v>180</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>2.822803874206545e-06</v>
+        <v>5.434578179757603e-09</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3012,58 +3012,58 @@
         <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
+        <v>7</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
         <v>25</v>
       </c>
-      <c r="I35" t="n">
-        <v>12</v>
-      </c>
-      <c r="J35" t="n">
-        <v>4</v>
-      </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M35" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="O35" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Q35" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="U35" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="W35" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36">
@@ -3071,13 +3071,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>114.8</v>
+        <v>57.6</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9932975139501152</v>
+        <v>0.9945314650016144</v>
       </c>
       <c r="D36" t="n">
-        <v>6.80902433051883e-06</v>
+        <v>6.085463548753202e-08</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3086,16 +3086,16 @@
         <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3107,37 +3107,37 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -3145,13 +3145,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>1265.6</v>
+        <v>56.8</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0.9883514764524332</v>
       </c>
       <c r="D37" t="n">
-        <v>3.245679753264286e-07</v>
+        <v>5.554819061410212e-08</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -3160,58 +3160,58 @@
         <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>139</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="M37" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Q37" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S37" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U37" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -3219,13 +3219,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>479.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0.9865401057916079</v>
       </c>
       <c r="D38" t="n">
-        <v>3.21415830388925e-06</v>
+        <v>4.812131573745923e-08</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -3234,58 +3234,58 @@
         <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I38" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M38" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O38" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Q38" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U38" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W38" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -3293,73 +3293,73 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>132.4</v>
+        <v>53.6</v>
       </c>
       <c r="C39" t="n">
-        <v>0.997148603744656</v>
+        <v>0.997233024517562</v>
       </c>
       <c r="D39" t="n">
-        <v>6.76714027104159e-06</v>
+        <v>8.676692423454717e-08</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -3367,73 +3367,73 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>840.8</v>
+        <v>53.6</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>0.9860015288401378</v>
       </c>
       <c r="D40" t="n">
-        <v>1.451524646930897e-06</v>
+        <v>6.338865617849984e-08</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>4</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>15</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
         <v>9</v>
       </c>
-      <c r="H40" t="n">
-        <v>68</v>
-      </c>
-      <c r="I40" t="n">
-        <v>17</v>
-      </c>
-      <c r="J40" t="n">
-        <v>12</v>
-      </c>
-      <c r="K40" t="n">
-        <v>7</v>
-      </c>
-      <c r="L40" t="n">
-        <v>10</v>
-      </c>
-      <c r="M40" t="n">
-        <v>20</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
       <c r="O40" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="W40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -3441,13 +3441,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>1198</v>
+        <v>195.2</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>5.598895563267332e-07</v>
+        <v>3.032241357161511e-09</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -3456,58 +3456,58 @@
         <v>2</v>
       </c>
       <c r="G41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M41" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="O41" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>16</v>
       </c>
       <c r="Q41" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="S41" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="U41" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="W41" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42">
@@ -3515,13 +3515,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>78.80000000000001</v>
+        <v>44</v>
       </c>
       <c r="C42" t="n">
-        <v>0.982484485408707</v>
+        <v>0.9782035132807106</v>
       </c>
       <c r="D42" t="n">
-        <v>7.308670936133949e-06</v>
+        <v>7.074232544948052e-08</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -3533,13 +3533,13 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3554,10 +3554,10 @@
         <v>6</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3575,13 +3575,13 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -3589,13 +3589,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>762.4</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>0.9918994793676464</v>
       </c>
       <c r="D43" t="n">
-        <v>1.664600109560413e-06</v>
+        <v>7.545408916321547e-08</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -3604,58 +3604,58 @@
         <v>2</v>
       </c>
       <c r="G43" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>18</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>15</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
         <v>5</v>
       </c>
-      <c r="L43" t="n">
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="M43" t="n">
-        <v>19</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>12</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>14</v>
-      </c>
-      <c r="R43" t="n">
-        <v>6</v>
-      </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>6</v>
       </c>
       <c r="U43" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="W43" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -3663,13 +3663,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>731.6</v>
+        <v>153.2</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1.850503606890214e-06</v>
+        <v>9.361381661949068e-09</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -3678,58 +3678,58 @@
         <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
+        <v>15</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>39</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>30</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
         <v>8</v>
       </c>
-      <c r="M44" t="n">
-        <v>15</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>12</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>14</v>
-      </c>
-      <c r="R44" t="n">
-        <v>6</v>
-      </c>
-      <c r="S44" t="n">
-        <v>12</v>
-      </c>
-      <c r="T44" t="n">
-        <v>6</v>
-      </c>
       <c r="U44" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="W44" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
@@ -3737,73 +3737,73 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>1379.2</v>
+        <v>43.2</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0.9769874938774331</v>
       </c>
       <c r="D45" t="n">
-        <v>2.826959289382508e-07</v>
+        <v>7.164940569285091e-08</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>139</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M45" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="O45" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="Q45" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U45" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="W45" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3811,73 +3811,73 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>1410.4</v>
+        <v>128.8</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>2.215912604144448e-07</v>
+        <v>1.544473490293021e-08</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>16</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>15</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>35</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
         <v>9</v>
       </c>
-      <c r="H46" t="n">
-        <v>140</v>
-      </c>
-      <c r="I46" t="n">
-        <v>25</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>12</v>
-      </c>
-      <c r="L46" t="n">
-        <v>22</v>
-      </c>
-      <c r="M46" t="n">
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>8</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
         <v>27</v>
       </c>
-      <c r="N46" t="n">
-        <v>54</v>
-      </c>
-      <c r="O46" t="n">
-        <v>15</v>
-      </c>
-      <c r="P46" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>22</v>
-      </c>
-      <c r="R46" t="n">
-        <v>65</v>
-      </c>
-      <c r="S46" t="n">
-        <v>20</v>
-      </c>
-      <c r="T46" t="n">
-        <v>10</v>
-      </c>
       <c r="U46" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="W46" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3885,13 +3885,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>249.2</v>
+        <v>85.2</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0.9895746940545764</v>
       </c>
       <c r="D47" t="n">
-        <v>5.20330557979033e-06</v>
+        <v>3.035582690279413e-08</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -3900,58 +3900,58 @@
         <v>2</v>
       </c>
       <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>15</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>26</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
         <v>5</v>
       </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>8</v>
-      </c>
-      <c r="J47" t="n">
-        <v>4</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>17</v>
-      </c>
-      <c r="M47" t="n">
-        <v>7</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>6</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
+        <v>5</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
         <v>12</v>
       </c>
-      <c r="S47" t="n">
-        <v>1</v>
-      </c>
-      <c r="T47" t="n">
-        <v>7</v>
-      </c>
       <c r="U47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="W47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3959,13 +3959,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>142.4</v>
+        <v>52</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9951093321933696</v>
+        <v>0.9834061986598266</v>
       </c>
       <c r="D48" t="n">
-        <v>6.537731842168095e-06</v>
+        <v>6.41512305176446e-08</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -3974,16 +3974,16 @@
         <v>2</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -3992,40 +3992,40 @@
         <v>15</v>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="U48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -4033,13 +4033,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>1086.4</v>
+        <v>142</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>6.194105283644955e-07</v>
+        <v>1.264873322487526e-08</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -4048,58 +4048,58 @@
         <v>2</v>
       </c>
       <c r="G49" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>129</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K49" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M49" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="O49" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q49" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="S49" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="U49" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
         <v>18</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -4107,73 +4107,73 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>1504.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0.9757714744741556</v>
       </c>
       <c r="D50" t="n">
-        <v>1.564076074484181e-07</v>
+        <v>7.26432956248026e-08</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="M50" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="O50" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="Q50" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="S50" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="U50" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="W50" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -4181,13 +4181,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>664</v>
+        <v>96.8</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0.9965554244948265</v>
       </c>
       <c r="D51" t="n">
-        <v>2.176571753636666e-06</v>
+        <v>2.301269397919649e-08</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -4196,58 +4196,58 @@
         <v>2</v>
       </c>
       <c r="G51" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M51" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O51" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q51" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U51" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="W51" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="X51" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -4255,13 +4255,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>62.40000000000001</v>
+        <v>176</v>
       </c>
       <c r="C52" t="n">
-        <v>0.982679998266476</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>7.709903714349441e-06</v>
+        <v>6.864082271914246e-09</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -4273,13 +4273,13 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -4291,37 +4291,37 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="O52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="W52" t="n">
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53">
@@ -4329,13 +4329,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>162.4</v>
+        <v>200.8</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9954626494439118</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>6.104440653859214e-06</v>
+        <v>2.424846138935862e-09</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -4344,16 +4344,16 @@
         <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -4362,40 +4362,40 @@
         <v>15</v>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="O53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="U53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="W53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54">
@@ -4403,13 +4403,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>436.8</v>
+        <v>96</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>0.999806606176125</v>
       </c>
       <c r="D54" t="n">
-        <v>3.572080528919034e-06</v>
+        <v>4.242825292358376e-08</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -4418,58 +4418,58 @@
         <v>2</v>
       </c>
       <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>10</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>15</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>33</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
         <v>8</v>
       </c>
-      <c r="H54" t="n">
-        <v>10</v>
-      </c>
-      <c r="I54" t="n">
-        <v>12</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>3</v>
-      </c>
-      <c r="L54" t="n">
-        <v>9</v>
-      </c>
-      <c r="M54" t="n">
-        <v>10</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>6</v>
-      </c>
-      <c r="P54" t="n">
-        <v>14</v>
-      </c>
       <c r="Q54" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
         <v>5</v>
       </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
       <c r="U54" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W54" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -4477,13 +4477,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>76.40000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9909833518010778</v>
+        <v>0.9826371333717356</v>
       </c>
       <c r="D55" t="n">
-        <v>7.431179442418781e-06</v>
+        <v>7.451551149075107e-08</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -4495,10 +4495,10 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
@@ -4513,13 +4513,13 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4534,10 +4534,10 @@
         <v>6</v>
       </c>
       <c r="U55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W55" t="n">
         <v>0</v>
@@ -4551,13 +4551,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>883.6</v>
+        <v>56</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>1.310652420436977e-06</v>
+        <v>7.832606297037463e-08</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -4566,58 +4566,58 @@
         <v>3</v>
       </c>
       <c r="G56" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="M56" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="O56" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q56" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="S56" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U56" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W56" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -4625,13 +4625,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>74.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9816732086822603</v>
+        <v>0.9872491391068099</v>
       </c>
       <c r="D57" t="n">
-        <v>7.423139145646379e-06</v>
+        <v>4.566615079842246e-08</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -4646,10 +4646,10 @@
         <v>2</v>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
         <v>15</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -4682,16 +4682,16 @@
         <v>6</v>
       </c>
       <c r="U57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -4699,13 +4699,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>219.6</v>
+        <v>60.8</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9987649064989075</v>
+        <v>0.9888040237763805</v>
       </c>
       <c r="D58" t="n">
-        <v>5.646876536698022e-06</v>
+        <v>5.193593636349844e-08</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -4714,58 +4714,58 @@
         <v>2</v>
       </c>
       <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>9</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>15</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="n">
         <v>4</v>
       </c>
-      <c r="H58" t="n">
-        <v>1</v>
-      </c>
-      <c r="I58" t="n">
-        <v>4</v>
-      </c>
-      <c r="J58" t="n">
-        <v>18</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>15</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2</v>
-      </c>
-      <c r="N58" t="n">
-        <v>7</v>
-      </c>
       <c r="O58" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="U58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
         <v>3</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4773,13 +4773,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>83.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="C59" t="n">
-        <v>0.985390788607823</v>
+        <v>0.9960868090970696</v>
       </c>
       <c r="D59" t="n">
-        <v>7.29297778563315e-06</v>
+        <v>4.307178474065266e-08</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -4791,13 +4791,13 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -4806,40 +4806,40 @@
         <v>15</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N59" t="n">
         <v>6</v>
       </c>
       <c r="O59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="W59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -4847,73 +4847,73 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>921.2</v>
+        <v>44</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>0.9782035132807106</v>
       </c>
       <c r="D60" t="n">
-        <v>1.088329643491867e-06</v>
+        <v>7.074232544948052e-08</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>2</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
         <v>3</v>
       </c>
-      <c r="G60" t="n">
-        <v>7</v>
-      </c>
-      <c r="H60" t="n">
-        <v>101</v>
-      </c>
-      <c r="I60" t="n">
-        <v>19</v>
-      </c>
-      <c r="J60" t="n">
-        <v>6</v>
-      </c>
       <c r="K60" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M60" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O60" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q60" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="S60" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="U60" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W60" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -4921,13 +4921,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>306</v>
+        <v>97.2</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>0.998327272260817</v>
       </c>
       <c r="D61" t="n">
-        <v>4.80345988624086e-06</v>
+        <v>3.89519355985199e-08</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -4936,58 +4936,58 @@
         <v>2</v>
       </c>
       <c r="G61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M61" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O61" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="U61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="W61" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -4995,13 +4995,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>194.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9976037517994965</v>
+        <v>0.9904757127917957</v>
       </c>
       <c r="D62" t="n">
-        <v>5.856573318408433e-06</v>
+        <v>4.401067089530055e-08</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -5010,58 +5010,58 @@
         <v>2</v>
       </c>
       <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>14</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>15</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>6</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>5</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>12</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>7</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
         <v>4</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>6</v>
-      </c>
-      <c r="J62" t="n">
-        <v>18</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>15</v>
-      </c>
-      <c r="M62" t="n">
-        <v>2</v>
-      </c>
-      <c r="N62" t="n">
-        <v>2</v>
-      </c>
-      <c r="O62" t="n">
-        <v>4</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>18</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>15</v>
-      </c>
-      <c r="U62" t="n">
-        <v>5</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1</v>
-      </c>
-      <c r="W62" t="n">
-        <v>2</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -5069,13 +5069,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>59.2</v>
+        <v>91.60000000000001</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9862604376367289</v>
+        <v>0.9913276212376754</v>
       </c>
       <c r="D63" t="n">
-        <v>7.818133896312442e-06</v>
+        <v>2.664141109032558e-08</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -5087,10 +5087,10 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>2</v>
@@ -5099,43 +5099,43 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="O63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -5143,13 +5143,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>171.2</v>
+        <v>60</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9993738629845612</v>
+        <v>0.9958193469264783</v>
       </c>
       <c r="D64" t="n">
-        <v>6.325029068929128e-06</v>
+        <v>5.879308714337928e-08</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -5158,16 +5158,16 @@
         <v>2</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -5176,40 +5176,40 @@
         <v>15</v>
       </c>
       <c r="M64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="U64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -5217,13 +5217,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>89.59999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9860602986602206</v>
+        <v>0.9958193469264783</v>
       </c>
       <c r="D65" t="n">
-        <v>7.2385957456268e-06</v>
+        <v>5.813225909895388e-08</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -5235,13 +5235,13 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -5253,37 +5253,37 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
+        <v>7</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
         <v>11</v>
       </c>
-      <c r="O65" t="n">
-        <v>2</v>
-      </c>
-      <c r="P65" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7</v>
-      </c>
       <c r="S65" t="n">
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -5291,13 +5291,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>63.2</v>
+        <v>118.4</v>
       </c>
       <c r="C66" t="n">
-        <v>0.9810286928717652</v>
+        <v>0.9997053348317577</v>
       </c>
       <c r="D66" t="n">
-        <v>7.588238254827351e-06</v>
+        <v>1.814270780424305e-08</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -5312,10 +5312,10 @@
         <v>3</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -5327,37 +5327,37 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="O66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="W66" t="n">
         <v>1</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -5365,13 +5365,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>63.6</v>
+        <v>77.2</v>
       </c>
       <c r="C67" t="n">
-        <v>0.98514497794011</v>
+        <v>0.9982788062427417</v>
       </c>
       <c r="D67" t="n">
-        <v>7.626318926148219e-06</v>
+        <v>4.73180460030085e-08</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -5383,13 +5383,13 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -5401,37 +5401,37 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="W67" t="n">
         <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68">
@@ -5439,13 +5439,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>207.6</v>
+        <v>56</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9983900503111769</v>
+        <v>0.9873351010834138</v>
       </c>
       <c r="D68" t="n">
-        <v>5.775274496513336e-06</v>
+        <v>5.672179285494081e-08</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -5454,58 +5454,58 @@
         <v>2</v>
       </c>
       <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>15</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" t="n">
+        <v>6</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>6</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>7</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
         <v>4</v>
-      </c>
-      <c r="H68" t="n">
-        <v>1</v>
-      </c>
-      <c r="I68" t="n">
-        <v>4</v>
-      </c>
-      <c r="J68" t="n">
-        <v>18</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>15</v>
-      </c>
-      <c r="M68" t="n">
-        <v>2</v>
-      </c>
-      <c r="N68" t="n">
-        <v>7</v>
-      </c>
-      <c r="O68" t="n">
-        <v>4</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>43</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>15</v>
-      </c>
-      <c r="U68" t="n">
-        <v>4</v>
-      </c>
-      <c r="V68" t="n">
-        <v>1</v>
-      </c>
-      <c r="W68" t="n">
-        <v>3</v>
-      </c>
-      <c r="X68" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -5513,13 +5513,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>577.2</v>
+        <v>154.8</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>2.665414449306463e-06</v>
+        <v>9.120494802412377e-09</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -5528,58 +5528,58 @@
         <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="I69" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>39</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
         <v>11</v>
       </c>
-      <c r="N69" t="n">
-        <v>1</v>
-      </c>
-      <c r="O69" t="n">
-        <v>11</v>
-      </c>
-      <c r="P69" t="n">
-        <v>3</v>
-      </c>
       <c r="Q69" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
         <v>8</v>
       </c>
-      <c r="T69" t="n">
-        <v>17</v>
-      </c>
       <c r="U69" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="W69" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70">
@@ -5587,13 +5587,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>62.40000000000001</v>
+        <v>132</v>
       </c>
       <c r="C70" t="n">
-        <v>0.9784276935330058</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>7.583987428406683e-06</v>
+        <v>1.418773589113887e-08</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -5605,13 +5605,13 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -5623,31 +5623,31 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="O70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="W70" t="n">
         <v>1</v>
@@ -5661,13 +5661,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>154.4</v>
+        <v>49.6</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9957519035163713</v>
+        <v>0.990531607671014</v>
       </c>
       <c r="D71" t="n">
-        <v>6.46091218279016e-06</v>
+        <v>7.738513772680517e-08</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -5676,37 +5676,37 @@
         <v>2</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O71" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>9</v>
@@ -5715,19 +5715,19 @@
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="U71" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -5735,13 +5735,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>64</v>
+        <v>109.6</v>
       </c>
       <c r="C72" t="n">
-        <v>0.9817487926995515</v>
+        <v>0.9989058094488751</v>
       </c>
       <c r="D72" t="n">
-        <v>7.576433394290879e-06</v>
+        <v>2.189691576422475e-08</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -5753,13 +5753,13 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -5771,37 +5771,37 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
+        <v>25</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1</v>
+      </c>
+      <c r="R72" t="n">
         <v>8</v>
       </c>
-      <c r="O72" t="n">
-        <v>2</v>
-      </c>
-      <c r="P72" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7</v>
-      </c>
       <c r="S72" t="n">
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="W72" t="n">
         <v>1</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -5809,13 +5809,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>368</v>
+        <v>112.8</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>0.999151645621209</v>
       </c>
       <c r="D73" t="n">
-        <v>4.07576915846503e-06</v>
+        <v>2.076537603866012e-08</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -5824,16 +5824,16 @@
         <v>2</v>
       </c>
       <c r="G73" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I73" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -5842,40 +5842,40 @@
         <v>15</v>
       </c>
       <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>26</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1</v>
+      </c>
+      <c r="R73" t="n">
         <v>8</v>
       </c>
-      <c r="N73" t="n">
-        <v>2</v>
-      </c>
-      <c r="O73" t="n">
-        <v>8</v>
-      </c>
-      <c r="P73" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>7</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="W73" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -5883,19 +5883,19 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>60.40000000000001</v>
+        <v>53.6</v>
       </c>
       <c r="C74" t="n">
-        <v>0.980141048746788</v>
+        <v>0.9970102583526685</v>
       </c>
       <c r="D74" t="n">
-        <v>7.655612880715803e-06</v>
+        <v>8.405538465429286e-08</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -5904,16 +5904,16 @@
         <v>2</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -5922,28 +5922,28 @@
         <v>6</v>
       </c>
       <c r="O74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W74" t="n">
         <v>0</v>
@@ -5957,73 +5957,73 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>889.6</v>
+        <v>79.2</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0.9924205442039714</v>
       </c>
       <c r="D75" t="n">
-        <v>1.27451262454595e-06</v>
+        <v>3.568474360967849e-08</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G75" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="I75" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K75" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M75" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="N75" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="O75" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q75" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="S75" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U75" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="V75" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W75" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -6031,13 +6031,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>68.40000000000001</v>
+        <v>106.8</v>
       </c>
       <c r="C76" t="n">
-        <v>0.9807044409492216</v>
+        <v>0.9993888148331866</v>
       </c>
       <c r="D76" t="n">
-        <v>7.460502214503202e-06</v>
+        <v>3.385952309794057e-08</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -6049,13 +6049,13 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -6067,37 +6067,37 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="O76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
       </c>
       <c r="V76" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="W76" t="n">
         <v>1</v>
       </c>
       <c r="X76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -6105,73 +6105,73 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>1616.4</v>
+        <v>48</v>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>0.9876116915524221</v>
       </c>
       <c r="D77" t="n">
-        <v>3.620739959093242e-08</v>
+        <v>8.210799714237648e-08</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G77" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>174</v>
+        <v>6</v>
       </c>
       <c r="I77" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K77" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="M77" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="O77" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="Q77" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="U77" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="W77" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -6179,13 +6179,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>963.6</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>0.9976505990574651</v>
       </c>
       <c r="D78" t="n">
-        <v>9.737368183369542e-07</v>
+        <v>2.487286099205302e-08</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -6194,58 +6194,58 @@
         <v>2</v>
       </c>
       <c r="G78" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K78" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M78" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="O78" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q78" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="S78" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U78" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V78" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="W78" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="X78" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -6253,13 +6253,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>104</v>
+        <v>53.6</v>
       </c>
       <c r="C79" t="n">
-        <v>0.9906332695458708</v>
+        <v>0.9860015288401378</v>
       </c>
       <c r="D79" t="n">
-        <v>7.025585206569077e-06</v>
+        <v>6.338865617849984e-08</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -6268,58 +6268,58 @@
         <v>2</v>
       </c>
       <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
         <v>4</v>
       </c>
-      <c r="H79" t="n">
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>15</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>9</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>6</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>9</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
         <v>8</v>
-      </c>
-      <c r="I79" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="n">
-        <v>15</v>
-      </c>
-      <c r="M79" t="n">
-        <v>2</v>
-      </c>
-      <c r="N79" t="n">
-        <v>8</v>
-      </c>
-      <c r="O79" t="n">
-        <v>2</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>8</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>6</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" t="n">
-        <v>7</v>
-      </c>
-      <c r="W79" t="n">
-        <v>1</v>
-      </c>
-      <c r="X79" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -6327,73 +6327,73 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>912.4</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>0.9847359087073391</v>
       </c>
       <c r="D80" t="n">
-        <v>1.10212520951395e-06</v>
+        <v>6.489805375137738e-08</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>5</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>15</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>9</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>6</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>9</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
         <v>3</v>
-      </c>
-      <c r="G80" t="n">
-        <v>7</v>
-      </c>
-      <c r="H80" t="n">
-        <v>101</v>
-      </c>
-      <c r="I80" t="n">
-        <v>19</v>
-      </c>
-      <c r="J80" t="n">
-        <v>6</v>
-      </c>
-      <c r="K80" t="n">
-        <v>8</v>
-      </c>
-      <c r="L80" t="n">
-        <v>3</v>
-      </c>
-      <c r="M80" t="n">
-        <v>21</v>
-      </c>
-      <c r="N80" t="n">
-        <v>4</v>
-      </c>
-      <c r="O80" t="n">
-        <v>16</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>16</v>
-      </c>
-      <c r="R80" t="n">
-        <v>25</v>
-      </c>
-      <c r="S80" t="n">
-        <v>14</v>
-      </c>
-      <c r="T80" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" t="n">
-        <v>16</v>
-      </c>
-      <c r="V80" t="n">
-        <v>0</v>
-      </c>
-      <c r="W80" t="n">
-        <v>16</v>
-      </c>
-      <c r="X80" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -6401,13 +6401,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>640.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>0.9865401057916079</v>
       </c>
       <c r="D81" t="n">
-        <v>2.45671503019169e-06</v>
+        <v>4.812131573745923e-08</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -6416,58 +6416,58 @@
         <v>2</v>
       </c>
       <c r="G81" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
         <v>14</v>
       </c>
-      <c r="J81" t="n">
-        <v>13</v>
-      </c>
       <c r="K81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M81" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="N81" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O81" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q81" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R81" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="U81" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W81" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
@@ -6475,13 +6475,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>756.4</v>
+        <v>118</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>1.72711636914933e-06</v>
+        <v>3.540120084696045e-08</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -6490,58 +6490,58 @@
         <v>2</v>
       </c>
       <c r="G82" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>15</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>46</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
         <v>5</v>
       </c>
-      <c r="L82" t="n">
-        <v>8</v>
-      </c>
-      <c r="M82" t="n">
-        <v>19</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>12</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
       <c r="Q82" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S82" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="U82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="W82" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -6549,13 +6549,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>168</v>
+        <v>48</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9961195955817086</v>
+        <v>0.9827062374235123</v>
       </c>
       <c r="D83" t="n">
-        <v>6.358650044079984e-06</v>
+        <v>6.694569452161251e-08</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -6564,16 +6564,16 @@
         <v>2</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -6582,40 +6582,40 @@
         <v>15</v>
       </c>
       <c r="M83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O83" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="U83" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W83" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -6623,13 +6623,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>126</v>
+        <v>83.60000000000001</v>
       </c>
       <c r="C84" t="n">
-        <v>0.9954916773672178</v>
+        <v>0.9948480311711823</v>
       </c>
       <c r="D84" t="n">
-        <v>6.964099065944556e-06</v>
+        <v>3.255998628656323e-08</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -6641,43 +6641,43 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I84" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>15</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>25</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
         <v>5</v>
       </c>
-      <c r="J84" t="n">
-        <v>1</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>15</v>
-      </c>
-      <c r="M84" t="n">
-        <v>1</v>
-      </c>
-      <c r="N84" t="n">
-        <v>6</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="n">
-        <v>21</v>
-      </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -6686,10 +6686,10 @@
         <v>14</v>
       </c>
       <c r="W84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -6697,13 +6697,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>654.8</v>
+        <v>145.2</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>2.358567730695942e-06</v>
+        <v>1.119929752467087e-08</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -6712,58 +6712,58 @@
         <v>2</v>
       </c>
       <c r="G85" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="I85" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M85" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O85" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q85" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S85" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U85" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="W85" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86">
@@ -6771,13 +6771,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>68.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="C86" t="n">
-        <v>0.99437786677295</v>
+        <v>0.9967641636680984</v>
       </c>
       <c r="D86" t="n">
-        <v>7.652108024955697e-06</v>
+        <v>3.561467273221859e-08</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -6792,49 +6792,49 @@
         <v>2</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X86" t="n">
         <v>2</v>
@@ -6845,13 +6845,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>225.2</v>
+        <v>45.6</v>
       </c>
       <c r="C87" t="n">
-        <v>0.9992894017354761</v>
+        <v>0.9806355520872658</v>
       </c>
       <c r="D87" t="n">
-        <v>5.38656658786849e-06</v>
+        <v>6.918859402848369e-08</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -6860,17 +6860,17 @@
         <v>2</v>
       </c>
       <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
         <v>5</v>
       </c>
-      <c r="H87" t="n">
-        <v>3</v>
-      </c>
-      <c r="I87" t="n">
-        <v>6</v>
-      </c>
-      <c r="J87" t="n">
-        <v>10</v>
-      </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
@@ -6878,40 +6878,40 @@
         <v>15</v>
       </c>
       <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>6</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
         <v>5</v>
       </c>
-      <c r="N87" t="n">
-        <v>1</v>
-      </c>
-      <c r="O87" t="n">
-        <v>4</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
       <c r="Q87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="U87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -6919,13 +6919,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>702.8</v>
+        <v>113.6</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>0.9991430505501622</v>
       </c>
       <c r="D88" t="n">
-        <v>1.933459568200433e-06</v>
+        <v>2.008941835571197e-08</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -6934,58 +6934,58 @@
         <v>2</v>
       </c>
       <c r="G88" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="I88" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M88" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="O88" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q88" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="R88" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="S88" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="U88" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="W88" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="X88" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -6993,13 +6993,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>189.6</v>
+        <v>44</v>
       </c>
       <c r="C89" t="n">
-        <v>0.9974091061308069</v>
+        <v>0.9801564709185774</v>
       </c>
       <c r="D89" t="n">
-        <v>5.904014535071661e-06</v>
+        <v>7.083994662389474e-08</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -7008,58 +7008,58 @@
         <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>15</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>7</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
         <v>5</v>
       </c>
-      <c r="J89" t="n">
-        <v>18</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>15</v>
-      </c>
-      <c r="M89" t="n">
-        <v>2</v>
-      </c>
-      <c r="N89" t="n">
-        <v>2</v>
-      </c>
-      <c r="O89" t="n">
-        <v>4</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="U89" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -7067,13 +7067,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>240</v>
+        <v>106</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>0.9992951007862541</v>
       </c>
       <c r="D90" t="n">
-        <v>5.26449498843245e-06</v>
+        <v>3.361614011636308e-08</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -7082,34 +7082,34 @@
         <v>2</v>
       </c>
       <c r="G90" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I90" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M90" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O90" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -7118,22 +7118,22 @@
         <v>9</v>
       </c>
       <c r="S90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="U90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="W90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -7141,13 +7141,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>1056</v>
+        <v>82.8</v>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>0.9894225719291752</v>
       </c>
       <c r="D91" t="n">
-        <v>7.426211092375952e-07</v>
+        <v>3.227371929655033e-08</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -7156,58 +7156,58 @@
         <v>2</v>
       </c>
       <c r="G91" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>124</v>
+        <v>3</v>
       </c>
       <c r="I91" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M91" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="O91" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q91" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="R91" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="S91" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="U91" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="W91" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="X91" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -7215,13 +7215,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>479.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>0.991641112268413</v>
       </c>
       <c r="D92" t="n">
-        <v>3.21415830388925e-06</v>
+        <v>4.093632484666306e-08</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -7230,58 +7230,58 @@
         <v>2</v>
       </c>
       <c r="G92" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I92" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>18</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>1</v>
+      </c>
+      <c r="R92" t="n">
+        <v>5</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
         <v>11</v>
       </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" t="n">
-        <v>8</v>
-      </c>
-      <c r="P92" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>8</v>
-      </c>
-      <c r="R92" t="n">
-        <v>16</v>
-      </c>
-      <c r="S92" t="n">
-        <v>5</v>
-      </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
       <c r="U92" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W92" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -7289,73 +7289,73 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>1570.4</v>
+        <v>45.6</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0.9806355520872658</v>
       </c>
       <c r="D93" t="n">
-        <v>5.932936887528869e-08</v>
+        <v>6.918859402848369e-08</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G93" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>161</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K93" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="M93" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="O93" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="Q93" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="S93" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="U93" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="W93" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -7363,13 +7363,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>78</v>
+        <v>184.8</v>
       </c>
       <c r="C94" t="n">
-        <v>0.994582976607909</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>7.430762646584113e-06</v>
+        <v>4.600534944508746e-09</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -7381,13 +7381,13 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -7399,37 +7399,37 @@
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="O94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="U94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V94" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="W94" t="n">
         <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95">
@@ -7437,13 +7437,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>223.6</v>
+        <v>91.60000000000001</v>
       </c>
       <c r="C95" t="n">
-        <v>0.9989181276089422</v>
+        <v>0.9998702341886443</v>
       </c>
       <c r="D95" t="n">
-        <v>5.395530101009378e-06</v>
+        <v>4.30343143472315e-08</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -7452,58 +7452,58 @@
         <v>2</v>
       </c>
       <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>11</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>15</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>11</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
         <v>5</v>
       </c>
-      <c r="H95" t="n">
-        <v>3</v>
-      </c>
-      <c r="I95" t="n">
-        <v>6</v>
-      </c>
-      <c r="J95" t="n">
-        <v>10</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
-        <v>15</v>
-      </c>
-      <c r="M95" t="n">
-        <v>5</v>
-      </c>
-      <c r="N95" t="n">
-        <v>1</v>
-      </c>
-      <c r="O95" t="n">
-        <v>4</v>
-      </c>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
       <c r="Q95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R95" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
       </c>
       <c r="T95" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U95" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96">
@@ -7511,13 +7511,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>60.8</v>
+        <v>176.8</v>
       </c>
       <c r="C96" t="n">
-        <v>0.9898617942074546</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>7.73208589631786e-06</v>
+        <v>6.752675166154408e-09</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -7529,13 +7529,13 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -7547,37 +7547,37 @@
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="O96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
       </c>
       <c r="V96" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="W96" t="n">
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97">
@@ -7585,73 +7585,73 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>140</v>
+        <v>53.6</v>
       </c>
       <c r="C97" t="n">
-        <v>0.99981763996168</v>
+        <v>0.9970102583526685</v>
       </c>
       <c r="D97" t="n">
-        <v>6.583078111301433e-06</v>
+        <v>8.405538465429286e-08</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="Q97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -7659,73 +7659,73 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>1528</v>
+        <v>118.4</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>0.9997053348317577</v>
       </c>
       <c r="D98" t="n">
-        <v>8.347696809417796e-08</v>
+        <v>1.814270780424305e-08</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G98" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>158</v>
+        <v>3</v>
       </c>
       <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>15</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>15</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>29</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1</v>
+      </c>
+      <c r="R98" t="n">
+        <v>10</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>22</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" t="n">
         <v>24</v>
       </c>
-      <c r="J98" t="n">
-        <v>35</v>
-      </c>
-      <c r="K98" t="n">
-        <v>11</v>
-      </c>
-      <c r="L98" t="n">
-        <v>47</v>
-      </c>
-      <c r="M98" t="n">
-        <v>28</v>
-      </c>
-      <c r="N98" t="n">
-        <v>50</v>
-      </c>
-      <c r="O98" t="n">
-        <v>17</v>
-      </c>
-      <c r="P98" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>24</v>
-      </c>
-      <c r="R98" t="n">
-        <v>69</v>
-      </c>
-      <c r="S98" t="n">
-        <v>20</v>
-      </c>
-      <c r="T98" t="n">
-        <v>77</v>
-      </c>
-      <c r="U98" t="n">
-        <v>25</v>
-      </c>
-      <c r="V98" t="n">
-        <v>41</v>
-      </c>
       <c r="W98" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="X98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -7733,13 +7733,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>577.2</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>0.9823413437820173</v>
       </c>
       <c r="D99" t="n">
-        <v>2.665414449306463e-06</v>
+        <v>6.832074451889226e-08</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -7748,58 +7748,58 @@
         <v>2</v>
       </c>
       <c r="G99" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="I99" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M99" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O99" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q99" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S99" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="U99" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W99" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -7807,73 +7807,73 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>1568.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>0.9948480311711823</v>
       </c>
       <c r="D100" t="n">
-        <v>7.078424244396857e-08</v>
+        <v>3.18470202829735e-08</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G100" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>168</v>
+        <v>3</v>
       </c>
       <c r="I100" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" t="n">
+        <v>1</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>15</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
         <v>25</v>
       </c>
-      <c r="J100" t="n">
-        <v>23</v>
-      </c>
-      <c r="K100" t="n">
-        <v>13</v>
-      </c>
-      <c r="L100" t="n">
-        <v>46</v>
-      </c>
-      <c r="M100" t="n">
-        <v>30</v>
-      </c>
-      <c r="N100" t="n">
-        <v>57</v>
-      </c>
       <c r="O100" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="Q100" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="R100" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="U100" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="V100" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="W100" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="X100" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -7881,13 +7881,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>97.59999999999999</v>
+        <v>48.8</v>
       </c>
       <c r="C101" t="n">
-        <v>0.9902836287817174</v>
+        <v>0.9835067618222262</v>
       </c>
       <c r="D101" t="n">
-        <v>7.032579825102343e-06</v>
+        <v>6.627280674427369e-08</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -7896,17 +7896,17 @@
         <v>2</v>
       </c>
       <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
         <v>4</v>
       </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="n">
-        <v>1</v>
-      </c>
-      <c r="J101" t="n">
-        <v>0</v>
-      </c>
       <c r="K101" t="n">
         <v>0</v>
       </c>
@@ -7914,40 +7914,40 @@
         <v>15</v>
       </c>
       <c r="M101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
+        <v>9</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>6</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" t="n">
         <v>8</v>
       </c>
-      <c r="O101" t="n">
-        <v>2</v>
-      </c>
-      <c r="P101" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="n">
-        <v>8</v>
-      </c>
-      <c r="S101" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" t="n">
-        <v>6</v>
-      </c>
-      <c r="U101" t="n">
-        <v>0</v>
-      </c>
-      <c r="V101" t="n">
-        <v>7</v>
-      </c>
       <c r="W101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/results/tables/Pareto前沿解集.xlsx
+++ b/results/tables/Pareto前沿解集.xlsx
@@ -555,13 +555,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>42.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9757714744741556</v>
+        <v>0.9762558583406749</v>
       </c>
       <c r="D2" t="n">
-        <v>7.26432956248026e-08</v>
+        <v>1.092512206299997e-05</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -588,10 +588,10 @@
         <v>15</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -606,22 +606,22 @@
         <v>7</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -629,37 +629,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>52.8</v>
+        <v>60.8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.997233024517562</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.72980288141136e-08</v>
+        <v>1.350796459042793e-05</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -671,19 +671,19 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>9</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>8</v>
-      </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -695,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -703,13 +703,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9757714744741556</v>
+        <v>0.9934918682307929</v>
       </c>
       <c r="D4" t="n">
-        <v>7.26432956248026e-08</v>
+        <v>1.315847060871641e-05</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -739,25 +739,25 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
+        <v>7</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>6</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>5</v>
-      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -769,7 +769,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -777,73 +777,73 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>300.4</v>
+        <v>1058.4</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.183621452945349e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>36</v>
+      </c>
+      <c r="M5" t="n">
+        <v>22</v>
+      </c>
+      <c r="N5" t="n">
+        <v>103</v>
+      </c>
+      <c r="O5" t="n">
+        <v>14</v>
+      </c>
+      <c r="P5" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q5" t="n">
         <v>10</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>22</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>48</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>29</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>36</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V5" t="n">
-        <v>63</v>
+        <v>152</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X5" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -851,73 +851,73 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>296.4</v>
+        <v>109.6</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.9815056842512699</v>
       </c>
       <c r="D6" t="n">
-        <v>1.65888101154397e-09</v>
+        <v>1.018003240774357e-05</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V6" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -925,13 +925,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>205.6</v>
+        <v>98</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.9799504573157112</v>
       </c>
       <c r="D7" t="n">
-        <v>1.708130596477537e-09</v>
+        <v>1.080991232000539e-05</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -943,13 +943,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -958,40 +958,40 @@
         <v>15</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V7" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -999,13 +999,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>67.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9933943811092961</v>
+        <v>0.9787786066998262</v>
       </c>
       <c r="D8" t="n">
-        <v>5.024189151858325e-08</v>
+        <v>1.081680120283984e-05</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1023,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1032,40 +1032,40 @@
         <v>15</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1073,13 +1073,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>43.2</v>
+        <v>496.8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9811969337161628</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>7.194608099021132e-08</v>
+        <v>1.962430871125637e-06</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1106,40 +1106,40 @@
         <v>15</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="T9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1147,13 +1147,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>48.8</v>
+        <v>198</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9930371507944292</v>
+        <v>0.9960293824200843</v>
       </c>
       <c r="D10" t="n">
-        <v>8.134310360734383e-08</v>
+        <v>8.29752399998113e-06</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1177,43 +1177,43 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1221,13 +1221,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>98.80000000000001</v>
+        <v>390</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9983362808662395</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.715039472609959e-08</v>
+        <v>3.697547554608023e-06</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1239,13 +1239,13 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1254,37 +1254,37 @@
         <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T11" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V11" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>101.6</v>
+        <v>98.8</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9978708607215191</v>
+        <v>0.9971666463946318</v>
       </c>
       <c r="D12" t="n">
-        <v>2.955752501414561e-08</v>
+        <v>1.218756926875933e-05</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1313,13 +1313,13 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1328,37 +1328,37 @@
         <v>15</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>9</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>3</v>
@@ -1369,13 +1369,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>90</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9902230963278893</v>
+        <v>0.9772246260737136</v>
       </c>
       <c r="D13" t="n">
-        <v>2.70969701398583e-08</v>
+        <v>1.071092446321078e-05</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1387,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1402,10 +1402,10 @@
         <v>15</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1414,28 +1414,28 @@
         <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1443,73 +1443,73 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>164.4</v>
+        <v>573.2</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.913907659487443e-09</v>
+        <v>1.47539977033898e-06</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>32</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>15</v>
+      </c>
+      <c r="M14" t="n">
+        <v>17</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>10</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>12</v>
+      </c>
+      <c r="S14" t="n">
+        <v>22</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>24</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>12</v>
+      </c>
+      <c r="X14" t="n">
         <v>6</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>26</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>15</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>37</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>32</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>12</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>34</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -1517,73 +1517,73 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>123.2</v>
+        <v>689.6</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.600138619241858e-08</v>
+        <v>7.389889251922005e-07</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N15" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T15" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V15" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1591,19 +1591,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>49.6</v>
+        <v>611.2</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9837195333383197</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.567652485531559e-08</v>
+        <v>1.19137688497936e-06</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1615,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1624,40 +1624,40 @@
         <v>15</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N16" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V16" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -1665,73 +1665,73 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>58.40000000000001</v>
+        <v>717.6</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9945314650016144</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.02830539185563e-08</v>
+        <v>6.437057187278383e-07</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T17" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V17" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1739,13 +1739,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>44.8</v>
+        <v>114.8</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9847312922412765</v>
+        <v>0.9832836081756327</v>
       </c>
       <c r="D18" t="n">
-        <v>7.643090342215271e-08</v>
+        <v>1.063504503677495e-05</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1769,13 +1769,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1790,22 +1790,22 @@
         <v>7</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1813,73 +1813,73 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>59.2</v>
+        <v>829.2</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9952367285441565</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>5.954104703800702e-08</v>
+        <v>1.380926453185957e-07</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>18</v>
+      </c>
+      <c r="M19" t="n">
+        <v>23</v>
+      </c>
+      <c r="N19" t="n">
+        <v>51</v>
+      </c>
+      <c r="O19" t="n">
+        <v>14</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
         <v>9</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>15</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="T19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="V19" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1887,31 +1887,31 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>44.8</v>
+        <v>301.6</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9794195326839883</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>6.992205489469146e-08</v>
+        <v>5.652760570744134e-06</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1920,40 +1920,40 @@
         <v>15</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1961,13 +1961,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>47.2</v>
+        <v>478</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9850387065678776</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>7.278299868573341e-08</v>
+        <v>2.161475786090134e-06</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1979,13 +1979,13 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1994,40 +1994,40 @@
         <v>15</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="T21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2035,13 +2035,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>161.2</v>
+        <v>148.8</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0.9921501495573783</v>
       </c>
       <c r="D22" t="n">
-        <v>8.216727384572222e-09</v>
+        <v>9.572947927582917e-06</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -2053,13 +2053,13 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2068,40 +2068,40 @@
         <v>15</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V22" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -2109,13 +2109,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>86</v>
+        <v>121.6</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9900310604307805</v>
+        <v>0.9845158346515991</v>
       </c>
       <c r="D23" t="n">
-        <v>3.126955113980689e-08</v>
+        <v>9.937697636276445e-06</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2142,10 +2142,10 @@
         <v>15</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2154,22 +2154,22 @@
         <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
@@ -2183,31 +2183,31 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>46.40000000000001</v>
+        <v>170.4</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9823413437820173</v>
+        <v>0.9896038618049865</v>
       </c>
       <c r="D24" t="n">
-        <v>6.832074451889226e-08</v>
+        <v>8.943034658983071e-06</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2216,16 +2216,16 @@
         <v>15</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2234,19 +2234,19 @@
         <v>7</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
         <v>2</v>
@@ -2257,19 +2257,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>66.80000000000001</v>
+        <v>586.4</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9879689218672889</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.021170872908424e-08</v>
+        <v>1.314055955890616e-06</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2281,49 +2281,49 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
+        <v>32</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>15</v>
+      </c>
+      <c r="M25" t="n">
+        <v>17</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>11</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>15</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>11</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
       <c r="P25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>24</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>12</v>
+      </c>
+      <c r="X25" t="n">
         <v>6</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>15</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -2331,13 +2331,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>43.2</v>
+        <v>368</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9769874938774331</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>7.164940569285091e-08</v>
+        <v>4.031169829476576e-06</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -2349,13 +2349,13 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2364,40 +2364,40 @@
         <v>15</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2405,13 +2405,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>104</v>
+        <v>445.6</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9989058094488751</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>2.614172041022563e-08</v>
+        <v>2.577040133192862e-06</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -2423,13 +2423,13 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2438,40 +2438,40 @@
         <v>15</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N27" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T27" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="V27" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="X27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2479,13 +2479,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>63.6</v>
+        <v>139.6</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9921848831031561</v>
+        <v>0.9839073461499938</v>
       </c>
       <c r="D28" t="n">
-        <v>5.351702081668719e-08</v>
+        <v>9.325593508515637e-06</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -2503,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2512,10 +2512,10 @@
         <v>15</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2524,28 +2524,28 @@
         <v>5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2553,73 +2553,73 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>56</v>
+        <v>871.6</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9829260172104262</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>5.547424396635796e-08</v>
+        <v>6.700830092189374e-08</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="T29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="V29" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="X29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2627,13 +2627,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>191.2</v>
+        <v>347.6</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0.9985911734979618</v>
       </c>
       <c r="D30" t="n">
-        <v>3.920201700590394e-09</v>
+        <v>4.35308853974921e-06</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2645,13 +2645,13 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2660,40 +2660,40 @@
         <v>15</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N30" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T30" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V30" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X30" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2701,13 +2701,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>70.80000000000001</v>
+        <v>94</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9909210124406265</v>
+        <v>0.9793412616251669</v>
       </c>
       <c r="D31" t="n">
-        <v>4.563478570682803e-08</v>
+        <v>1.083570451883331e-05</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -2719,49 +2719,49 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
         <v>1</v>
@@ -2775,13 +2775,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>43.2</v>
+        <v>329.6</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9791400955495581</v>
+        <v>0.9984037454040966</v>
       </c>
       <c r="D32" t="n">
-        <v>7.184082407812808e-08</v>
+        <v>4.865828378484561e-06</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -2793,13 +2793,13 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2808,40 +2808,40 @@
         <v>15</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T32" t="n">
+        <v>12</v>
+      </c>
+      <c r="U32" t="n">
+        <v>11</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
         <v>6</v>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>7</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
       <c r="X32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2849,70 +2849,70 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>137.6</v>
+        <v>779.6</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>1.299551262335245e-08</v>
+        <v>2.371416312603739e-07</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J33" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N33" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P33" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R33" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
         <v>27</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
       <c r="V33" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -2923,73 +2923,73 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>78</v>
+        <v>631.2</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9925937587925283</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>4.034386388251058e-08</v>
+        <v>1.016633864680878e-06</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N34" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T34" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -2997,13 +2997,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>180</v>
+        <v>542.8</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>5.434578179757603e-09</v>
+        <v>1.81636643656121e-06</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3015,55 +3015,55 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N35" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P35" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="T35" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="V35" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X35" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
@@ -3071,31 +3071,31 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>57.6</v>
+        <v>271.2</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9945314650016144</v>
+        <v>0.9977843770878237</v>
       </c>
       <c r="D36" t="n">
-        <v>6.085463548753202e-08</v>
+        <v>5.941095238659145e-06</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3104,40 +3104,40 @@
         <v>15</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P36" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3145,13 +3145,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>56.8</v>
+        <v>548.8</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9883514764524332</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>5.554819061410212e-08</v>
+        <v>1.722310932850988e-06</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -3169,49 +3169,49 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P37" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="T37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="V37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X37" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
@@ -3219,73 +3219,73 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>66.40000000000001</v>
+        <v>972.4</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9865401057916079</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>4.812131573745923e-08</v>
+        <v>2.893333243592443e-08</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J38" t="n">
+        <v>18</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>25</v>
+      </c>
+      <c r="M38" t="n">
+        <v>22</v>
+      </c>
+      <c r="N38" t="n">
+        <v>92</v>
+      </c>
+      <c r="O38" t="n">
+        <v>13</v>
+      </c>
+      <c r="P38" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>10</v>
+      </c>
+      <c r="R38" t="n">
+        <v>4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>29</v>
+      </c>
+      <c r="T38" t="n">
         <v>14</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>15</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>7</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>5</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>6</v>
-      </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="V38" t="n">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="X38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3293,73 +3293,73 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>53.6</v>
+        <v>669.6</v>
       </c>
       <c r="C39" t="n">
-        <v>0.997233024517562</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>8.676692423454717e-08</v>
+        <v>9.023011759546737e-07</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="N39" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P39" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="T39" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3367,13 +3367,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>53.6</v>
+        <v>209.2</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9860015288401378</v>
+        <v>0.9918879300570189</v>
       </c>
       <c r="D40" t="n">
-        <v>6.338865617849984e-08</v>
+        <v>7.555951277351582e-06</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -3385,13 +3385,13 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -3400,16 +3400,16 @@
         <v>15</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
         <v>9</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3418,22 +3418,22 @@
         <v>7</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V40" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X40" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -3441,31 +3441,31 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>195.2</v>
+        <v>247.2</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>0.9983928655894291</v>
       </c>
       <c r="D41" t="n">
-        <v>3.032241357161511e-09</v>
+        <v>6.844993819080212e-06</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3477,37 +3477,37 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P41" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T41" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V41" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X41" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3515,73 +3515,73 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>44</v>
+        <v>747.2</v>
       </c>
       <c r="C42" t="n">
-        <v>0.9782035132807106</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>7.074232544948052e-08</v>
+        <v>6.277346154179769e-07</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N42" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P42" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R42" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V42" t="n">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="X42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3589,19 +3589,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>54.40000000000001</v>
+        <v>268.8</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9918994793676464</v>
+        <v>0.9991248839622326</v>
       </c>
       <c r="D43" t="n">
-        <v>7.545408916321547e-08</v>
+        <v>6.080250895397852e-06</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3613,49 +3613,49 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N43" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P43" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V43" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -3663,73 +3663,73 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>153.2</v>
+        <v>208.4</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>9.361381661949068e-09</v>
+        <v>7.736499337586118e-06</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T44" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V44" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -3737,31 +3737,31 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>43.2</v>
+        <v>254.8</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9769874938774331</v>
+        <v>0.9981966986458982</v>
       </c>
       <c r="D45" t="n">
-        <v>7.164940569285091e-08</v>
+        <v>6.329694816464317e-06</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -3770,40 +3770,40 @@
         <v>15</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N45" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P45" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3811,31 +3811,31 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>128.8</v>
+        <v>259.2</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0.9976091528524176</v>
       </c>
       <c r="D46" t="n">
-        <v>1.544473490293021e-08</v>
+        <v>6.254226389800855e-06</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -3844,37 +3844,37 @@
         <v>15</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N46" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P46" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
         <v>9</v>
       </c>
-      <c r="Q46" t="n">
-        <v>1</v>
-      </c>
-      <c r="R46" t="n">
-        <v>8</v>
-      </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T46" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V46" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -3885,28 +3885,28 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>85.2</v>
+        <v>164.8</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9895746940545764</v>
+        <v>0.9892979261363521</v>
       </c>
       <c r="D47" t="n">
-        <v>3.035582690279413e-08</v>
+        <v>8.773831643317824e-06</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -3918,40 +3918,40 @@
         <v>15</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T47" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V47" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="W47" t="n">
         <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3959,13 +3959,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>52</v>
+        <v>66.80000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9834061986598266</v>
+        <v>0.9952692023726225</v>
       </c>
       <c r="D48" t="n">
-        <v>6.41512305176446e-08</v>
+        <v>1.281322681807318e-05</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -3977,13 +3977,13 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -3995,25 +3995,25 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>7</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -4033,31 +4033,31 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>142</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0.9888161397087754</v>
       </c>
       <c r="D49" t="n">
-        <v>1.264873322487526e-08</v>
+        <v>1.137718729478435e-05</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -4066,40 +4066,40 @@
         <v>15</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T49" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4107,13 +4107,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>42.40000000000001</v>
+        <v>86.80000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9757714744741556</v>
+        <v>0.9858126391982245</v>
       </c>
       <c r="D50" t="n">
-        <v>7.26432956248026e-08</v>
+        <v>1.114531854477128e-05</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -4143,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -4158,22 +4158,22 @@
         <v>7</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T50" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V50" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4181,13 +4181,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>96.8</v>
+        <v>442</v>
       </c>
       <c r="C51" t="n">
-        <v>0.9965554244948265</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>2.301269397919649e-08</v>
+        <v>2.93982621051521e-06</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -4205,49 +4205,49 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
+        <v>15</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>15</v>
+      </c>
+      <c r="M51" t="n">
+        <v>15</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4</v>
+      </c>
+      <c r="O51" t="n">
+        <v>8</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>12</v>
+      </c>
+      <c r="S51" t="n">
+        <v>21</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>13</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
         <v>10</v>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>15</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" t="n">
-        <v>11</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1</v>
-      </c>
-      <c r="R51" t="n">
-        <v>6</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1</v>
-      </c>
-      <c r="T51" t="n">
-        <v>6</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>27</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1</v>
-      </c>
       <c r="X51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4255,13 +4255,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>176</v>
+        <v>308.8</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>0.999250780613902</v>
       </c>
       <c r="D52" t="n">
-        <v>6.864082271914246e-09</v>
+        <v>5.088406536193752e-06</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -4273,55 +4273,55 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
+        <v>4</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>7</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>15</v>
+      </c>
+      <c r="M52" t="n">
+        <v>9</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
         <v>8</v>
       </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>25</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>15</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>40</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
       <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
         <v>13</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>32</v>
-      </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T52" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V52" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X52" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4329,13 +4329,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>200.8</v>
+        <v>112</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0.9818894940068171</v>
       </c>
       <c r="D53" t="n">
-        <v>2.424846138935862e-09</v>
+        <v>1.03621182346268e-05</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -4347,13 +4347,13 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -4362,40 +4362,40 @@
         <v>15</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N53" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T53" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V53" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4403,13 +4403,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>96</v>
+        <v>112.8</v>
       </c>
       <c r="C54" t="n">
-        <v>0.999806606176125</v>
+        <v>0.9825166083550627</v>
       </c>
       <c r="D54" t="n">
-        <v>4.242825292358376e-08</v>
+        <v>1.057391001782514e-05</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -4436,40 +4436,40 @@
         <v>15</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T54" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V54" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -4477,73 +4477,73 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>44.8</v>
+        <v>890</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9826371333717356</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>7.451551149075107e-08</v>
+        <v>6.260027973791796e-08</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N55" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="T55" t="n">
         <v>6</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="V55" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="X55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -4551,46 +4551,46 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0.9966605171479188</v>
       </c>
       <c r="D56" t="n">
-        <v>7.832606297037463e-08</v>
+        <v>1.115932901173679e-05</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P56" t="n">
         <v>6</v>
@@ -4599,25 +4599,25 @@
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T56" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -4625,13 +4625,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>69.59999999999999</v>
+        <v>178.4</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9872491391068099</v>
+        <v>0.9914961384710246</v>
       </c>
       <c r="D57" t="n">
-        <v>4.566615079842246e-08</v>
+        <v>8.373872201437145e-06</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -4658,40 +4658,40 @@
         <v>15</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3</v>
+      </c>
+      <c r="P57" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
         <v>8</v>
       </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>1</v>
-      </c>
-      <c r="R57" t="n">
-        <v>5</v>
-      </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T57" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -4699,73 +4699,73 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>60.8</v>
+        <v>960.8</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9888040237763805</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>5.193593636349844e-08</v>
+        <v>3.898327323199255e-08</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J58" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="N58" t="n">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P58" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="Q58" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R58" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="T58" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="V58" t="n">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="X58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4773,19 +4773,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>72</v>
+        <v>646.8</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9960868090970696</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>4.307178474065266e-08</v>
+        <v>9.057725473534914e-07</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -4797,49 +4797,49 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
+        <v>27</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>15</v>
+      </c>
+      <c r="M59" t="n">
+        <v>20</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>12</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>5</v>
+      </c>
+      <c r="R59" t="n">
         <v>14</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>15</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1</v>
-      </c>
-      <c r="N59" t="n">
-        <v>6</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>6</v>
-      </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>24</v>
+      </c>
+      <c r="V59" t="n">
+        <v>9</v>
+      </c>
+      <c r="W59" t="n">
         <v>12</v>
       </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>7</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
       <c r="X59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -4847,73 +4847,73 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>44</v>
+        <v>1014.8</v>
       </c>
       <c r="C60" t="n">
-        <v>0.9782035132807106</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>7.074232544948052e-08</v>
+        <v>2.034383823590851e-08</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J60" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N60" t="n">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P60" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R60" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="T60" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V60" t="n">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -4921,13 +4921,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>97.2</v>
+        <v>338.8</v>
       </c>
       <c r="C61" t="n">
-        <v>0.998327272260817</v>
+        <v>0.999250780613902</v>
       </c>
       <c r="D61" t="n">
-        <v>3.89519355985199e-08</v>
+        <v>4.450067387819931e-06</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -4939,55 +4939,55 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
+        <v>7</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>15</v>
+      </c>
+      <c r="M61" t="n">
         <v>9</v>
       </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>15</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
       <c r="N61" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>13</v>
+      </c>
+      <c r="S61" t="n">
+        <v>17</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
         <v>11</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>9</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>15</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
       <c r="V61" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -4995,13 +4995,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>70.40000000000001</v>
+        <v>115.6</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9904757127917957</v>
+        <v>0.9838097778885559</v>
       </c>
       <c r="D62" t="n">
-        <v>4.401067089530055e-08</v>
+        <v>1.029332829122102e-05</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -5016,10 +5016,10 @@
         <v>2</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -5028,40 +5028,40 @@
         <v>15</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N62" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T62" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V62" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -5069,13 +5069,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>91.60000000000001</v>
+        <v>74</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9913276212376754</v>
+        <v>0.9953485204908624</v>
       </c>
       <c r="D63" t="n">
-        <v>2.664141109032558e-08</v>
+        <v>1.244832098503311e-05</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -5087,10 +5087,10 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>2</v>
@@ -5105,37 +5105,37 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V63" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="W63" t="n">
         <v>1</v>
       </c>
       <c r="X63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -5143,13 +5143,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>60</v>
+        <v>75.2</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9958193469264783</v>
+        <v>0.9966712724831612</v>
       </c>
       <c r="D64" t="n">
-        <v>5.879308714337928e-08</v>
+        <v>1.264819237582536e-05</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -5161,40 +5161,40 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
+        <v>4</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>15</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>18</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
         <v>9</v>
       </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>15</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
-        <v>7</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>10</v>
-      </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
         <v>7</v>
@@ -5203,13 +5203,13 @@
         <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X64" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5217,19 +5217,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>60.8</v>
+        <v>86.80000000000001</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9958193469264783</v>
+        <v>0.9866320801781313</v>
       </c>
       <c r="D65" t="n">
-        <v>5.813225909895388e-08</v>
+        <v>1.167774477860065e-05</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -5250,40 +5250,40 @@
         <v>15</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N65" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T65" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X65" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -5291,13 +5291,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>118.4</v>
+        <v>232</v>
       </c>
       <c r="C66" t="n">
-        <v>0.9997053348317577</v>
+        <v>0.9874883738020982</v>
       </c>
       <c r="D66" t="n">
-        <v>1.814270780424305e-08</v>
+        <v>7.212859247916308e-06</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -5315,7 +5315,7 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -5324,40 +5324,40 @@
         <v>15</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N66" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P66" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
+        <v>7</v>
+      </c>
+      <c r="S66" t="n">
+        <v>9</v>
+      </c>
+      <c r="T66" t="n">
+        <v>20</v>
+      </c>
+      <c r="U66" t="n">
         <v>10</v>
       </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>22</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
       <c r="V66" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="W66" t="n">
         <v>1</v>
       </c>
       <c r="X66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -5365,13 +5365,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>77.2</v>
+        <v>221.2</v>
       </c>
       <c r="C67" t="n">
-        <v>0.9982788062427417</v>
+        <v>0.9931049070602296</v>
       </c>
       <c r="D67" t="n">
-        <v>4.73180460030085e-08</v>
+        <v>7.418095043056525e-06</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -5383,55 +5383,55 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>15</v>
+      </c>
+      <c r="M67" t="n">
+        <v>7</v>
+      </c>
+      <c r="N67" t="n">
+        <v>9</v>
+      </c>
+      <c r="O67" t="n">
+        <v>3</v>
+      </c>
+      <c r="P67" t="n">
         <v>8</v>
       </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>15</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
-        <v>11</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>5</v>
-      </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T67" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V67" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X67" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -5439,13 +5439,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>56</v>
+        <v>251.2</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9873351010834138</v>
+        <v>0.9931435549800464</v>
       </c>
       <c r="D68" t="n">
-        <v>5.672179285494081e-08</v>
+        <v>6.511164321345595e-06</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -5457,13 +5457,13 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -5472,40 +5472,40 @@
         <v>15</v>
       </c>
       <c r="M68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N68" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P68" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T68" t="n">
         <v>6</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V68" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -5513,13 +5513,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>154.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>0.9772246260737136</v>
       </c>
       <c r="D69" t="n">
-        <v>9.120494802412377e-09</v>
+        <v>1.071092446321078e-05</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -5531,13 +5531,13 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -5546,40 +5546,40 @@
         <v>15</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N69" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T69" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V69" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X69" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -5587,13 +5587,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>132</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>0.994358396763191</v>
       </c>
       <c r="D70" t="n">
-        <v>1.418773589113887e-08</v>
+        <v>1.144795962895494e-05</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -5605,13 +5605,13 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -5620,40 +5620,40 @@
         <v>15</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N70" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P70" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
         <v>9</v>
       </c>
-      <c r="Q70" t="n">
-        <v>1</v>
-      </c>
-      <c r="R70" t="n">
+      <c r="S70" t="n">
+        <v>3</v>
+      </c>
+      <c r="T70" t="n">
         <v>8</v>
       </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>27</v>
-      </c>
       <c r="U70" t="n">
         <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="W70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -5661,13 +5661,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>49.6</v>
+        <v>145.6</v>
       </c>
       <c r="C71" t="n">
-        <v>0.990531607671014</v>
+        <v>0.9845158346515991</v>
       </c>
       <c r="D71" t="n">
-        <v>7.738513772680517e-08</v>
+        <v>9.336282840865759e-06</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -5691,43 +5691,43 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N71" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T71" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V71" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -5735,13 +5735,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>109.6</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C72" t="n">
-        <v>0.9989058094488751</v>
+        <v>0.994963705074747</v>
       </c>
       <c r="D72" t="n">
-        <v>2.189691576422475e-08</v>
+        <v>1.344588262872565e-05</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -5753,13 +5753,13 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -5771,37 +5771,37 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="W72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -5809,73 +5809,73 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>112.8</v>
+        <v>926.4</v>
       </c>
       <c r="C73" t="n">
-        <v>0.999151645621209</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>2.076537603866012e-08</v>
+        <v>4.468868031820206e-08</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
+        <v>32</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>18</v>
+      </c>
+      <c r="M73" t="n">
+        <v>24</v>
+      </c>
+      <c r="N73" t="n">
+        <v>52</v>
+      </c>
+      <c r="O73" t="n">
         <v>14</v>
       </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>15</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
+      <c r="P73" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>10</v>
+      </c>
+      <c r="R73" t="n">
+        <v>3</v>
+      </c>
+      <c r="S73" t="n">
+        <v>29</v>
+      </c>
+      <c r="T73" t="n">
+        <v>6</v>
+      </c>
+      <c r="U73" t="n">
+        <v>29</v>
+      </c>
+      <c r="V73" t="n">
         <v>26</v>
       </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>1</v>
-      </c>
-      <c r="R73" t="n">
-        <v>8</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>21</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" t="n">
-        <v>24</v>
-      </c>
       <c r="W73" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="X73" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74">
@@ -5883,73 +5883,73 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>53.6</v>
+        <v>412.4</v>
       </c>
       <c r="C74" t="n">
-        <v>0.9970102583526685</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>8.405538465429286e-08</v>
+        <v>3.525726648328202e-06</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>5</v>
+      </c>
+      <c r="P74" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>13</v>
+      </c>
+      <c r="S74" t="n">
+        <v>18</v>
+      </c>
+      <c r="T74" t="n">
         <v>6</v>
       </c>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>8</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" t="n">
-        <v>8</v>
-      </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V74" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="X74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -5957,13 +5957,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>79.2</v>
+        <v>102</v>
       </c>
       <c r="C75" t="n">
-        <v>0.9924205442039714</v>
+        <v>0.9911473912409386</v>
       </c>
       <c r="D75" t="n">
-        <v>3.568474360967849e-08</v>
+        <v>1.136600762707972e-05</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -5981,49 +5981,49 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V75" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6031,28 +6031,28 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>106.8</v>
+        <v>1051.2</v>
       </c>
       <c r="C76" t="n">
-        <v>0.9993888148331866</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>3.385952309794057e-08</v>
+        <v>1.04427170522974e-08</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J76" t="n">
         <v>18</v>
@@ -6061,43 +6061,43 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N76" t="n">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P76" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R76" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="T76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V76" t="n">
-        <v>26</v>
+        <v>148</v>
       </c>
       <c r="W76" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="X76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -6105,13 +6105,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>48</v>
+        <v>428.4</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9876116915524221</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>8.210799714237648e-08</v>
+        <v>3.007704982090614e-06</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -6123,55 +6123,55 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
+        <v>2</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
         <v>6</v>
       </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" t="n">
-        <v>1</v>
-      </c>
       <c r="K77" t="n">
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N77" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P77" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T77" t="n">
+        <v>9</v>
+      </c>
+      <c r="U77" t="n">
+        <v>20</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
         <v>6</v>
       </c>
-      <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" t="n">
-        <v>7</v>
-      </c>
-      <c r="W77" t="n">
-        <v>0</v>
-      </c>
       <c r="X77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -6179,13 +6179,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>96.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="C78" t="n">
-        <v>0.9976505990574651</v>
+        <v>0.9762558583406749</v>
       </c>
       <c r="D78" t="n">
-        <v>2.487286099205302e-08</v>
+        <v>1.092512206299997e-05</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -6203,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -6212,40 +6212,40 @@
         <v>15</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N78" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T78" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V78" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="W78" t="n">
         <v>1</v>
       </c>
       <c r="X78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -6253,13 +6253,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>53.6</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="C79" t="n">
-        <v>0.9860015288401378</v>
+        <v>0.9956404764991562</v>
       </c>
       <c r="D79" t="n">
-        <v>6.338865617849984e-08</v>
+        <v>1.280306838022282e-05</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -6271,13 +6271,13 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -6289,37 +6289,37 @@
         <v>0</v>
       </c>
       <c r="N79" t="n">
+        <v>7</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
         <v>9</v>
       </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7</v>
-      </c>
       <c r="S79" t="n">
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X79" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -6327,13 +6327,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>50.40000000000001</v>
+        <v>419.2</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9847359087073391</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>6.489805375137738e-08</v>
+        <v>3.241752933464995e-06</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -6360,40 +6360,40 @@
         <v>15</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N80" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P80" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T80" t="n">
         <v>6</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V80" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -6401,13 +6401,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>66.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9865401057916079</v>
+        <v>0.9854200853451109</v>
       </c>
       <c r="D81" t="n">
-        <v>4.812131573745923e-08</v>
+        <v>1.082738540845729e-05</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -6425,7 +6425,7 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -6434,40 +6434,40 @@
         <v>15</v>
       </c>
       <c r="M81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N81" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V81" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -6475,13 +6475,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>0.9874883738020982</v>
       </c>
       <c r="D82" t="n">
-        <v>3.540120084696045e-08</v>
+        <v>7.410110596421742e-06</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -6499,7 +6499,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -6508,40 +6508,40 @@
         <v>15</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N82" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P82" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
+        <v>7</v>
+      </c>
+      <c r="S82" t="n">
+        <v>9</v>
+      </c>
+      <c r="T82" t="n">
+        <v>20</v>
+      </c>
+      <c r="U82" t="n">
         <v>10</v>
       </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>18</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0</v>
-      </c>
       <c r="V82" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="W82" t="n">
         <v>1</v>
       </c>
       <c r="X82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -6549,73 +6549,73 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>48</v>
+        <v>836.8</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9827062374235123</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>6.694569452161251e-08</v>
+        <v>1.325391034976255e-07</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J83" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="N83" t="n">
+        <v>52</v>
+      </c>
+      <c r="O83" t="n">
+        <v>14</v>
+      </c>
+      <c r="P83" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q83" t="n">
         <v>9</v>
       </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="T83" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="V83" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="X83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -6623,13 +6623,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>83.60000000000001</v>
+        <v>409.6</v>
       </c>
       <c r="C84" t="n">
-        <v>0.9948480311711823</v>
+        <v>0.9995577199331869</v>
       </c>
       <c r="D84" t="n">
-        <v>3.255998628656323e-08</v>
+        <v>3.189229325080213e-06</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -6641,13 +6641,13 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -6656,37 +6656,37 @@
         <v>15</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N84" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T84" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V84" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W84" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X84" t="n">
         <v>0</v>
@@ -6697,19 +6697,19 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>145.2</v>
+        <v>181.6</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0.9923403686443789</v>
       </c>
       <c r="D85" t="n">
-        <v>1.119929752467087e-08</v>
+        <v>8.613136231268827e-06</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -6721,7 +6721,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -6730,40 +6730,40 @@
         <v>15</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N85" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P85" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="S85" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T85" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V85" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="W85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X85" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -6771,19 +6771,19 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>80</v>
+        <v>197.6</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9967641636680984</v>
+        <v>0.9945745407579928</v>
       </c>
       <c r="D86" t="n">
-        <v>3.561467273221859e-08</v>
+        <v>7.733216992222619e-06</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -6795,49 +6795,49 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>19</v>
+      </c>
+      <c r="M86" t="n">
+        <v>3</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
+      </c>
+      <c r="P86" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7</v>
+      </c>
+      <c r="S86" t="n">
+        <v>13</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="n">
         <v>10</v>
       </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>15</v>
-      </c>
-      <c r="M86" t="n">
-        <v>1</v>
-      </c>
-      <c r="N86" t="n">
-        <v>13</v>
-      </c>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>1</v>
-      </c>
-      <c r="R86" t="n">
-        <v>6</v>
-      </c>
-      <c r="S86" t="n">
-        <v>1</v>
-      </c>
-      <c r="T86" t="n">
-        <v>5</v>
-      </c>
-      <c r="U86" t="n">
-        <v>0</v>
-      </c>
       <c r="V86" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W86" t="n">
         <v>1</v>
       </c>
       <c r="X86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -6845,13 +6845,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>45.6</v>
+        <v>472</v>
       </c>
       <c r="C87" t="n">
-        <v>0.9806355520872658</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>6.918859402848369e-08</v>
+        <v>2.466743577011754e-06</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -6869,7 +6869,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -6878,40 +6878,40 @@
         <v>15</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N87" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P87" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T87" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="V87" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X87" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88">
@@ -6919,13 +6919,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>113.6</v>
+        <v>110.4</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9991430505501622</v>
+        <v>0.986740952047156</v>
       </c>
       <c r="D88" t="n">
-        <v>2.008941835571197e-08</v>
+        <v>1.082040135286022e-05</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -6937,13 +6937,13 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -6952,10 +6952,10 @@
         <v>15</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N88" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -6964,28 +6964,28 @@
         <v>5</v>
       </c>
       <c r="Q88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T88" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V88" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="W88" t="n">
         <v>1</v>
       </c>
       <c r="X88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -6993,13 +6993,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>44</v>
+        <v>187.6</v>
       </c>
       <c r="C89" t="n">
-        <v>0.9801564709185774</v>
+        <v>0.993505061541055</v>
       </c>
       <c r="D89" t="n">
-        <v>7.083994662389474e-08</v>
+        <v>9.826968328769208e-06</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -7017,7 +7017,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -7026,10 +7026,10 @@
         <v>15</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N89" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -7044,22 +7044,22 @@
         <v>7</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T89" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V89" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="X89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -7067,73 +7067,73 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>106</v>
+        <v>758.8</v>
       </c>
       <c r="C90" t="n">
-        <v>0.9992951007862541</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>3.361614011636308e-08</v>
+        <v>4.692215924934452e-07</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J90" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N90" t="n">
+        <v>30</v>
+      </c>
+      <c r="O90" t="n">
+        <v>11</v>
+      </c>
+      <c r="P90" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>5</v>
+      </c>
+      <c r="R90" t="n">
+        <v>1</v>
+      </c>
+      <c r="S90" t="n">
         <v>25</v>
       </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="n">
-        <v>9</v>
-      </c>
-      <c r="S90" t="n">
-        <v>0</v>
-      </c>
       <c r="T90" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V90" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="W90" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="X90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -7141,13 +7141,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>82.8</v>
+        <v>177.6</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9894225719291752</v>
+        <v>0.9860706792290174</v>
       </c>
       <c r="D91" t="n">
-        <v>3.227371929655033e-08</v>
+        <v>8.371125444177647e-06</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -7159,10 +7159,10 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
         <v>1</v>
@@ -7174,37 +7174,37 @@
         <v>15</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>3</v>
+      </c>
+      <c r="P91" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="n">
         <v>25</v>
       </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>1</v>
-      </c>
-      <c r="R91" t="n">
-        <v>5</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>10</v>
-      </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V91" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X91" t="n">
         <v>0</v>
@@ -7215,28 +7215,28 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>76.40000000000001</v>
+        <v>771.6</v>
       </c>
       <c r="C92" t="n">
-        <v>0.991641112268413</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>4.093632484666306e-08</v>
+        <v>4.350622059121818e-07</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7245,40 +7245,40 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
+        <v>21</v>
+      </c>
+      <c r="M92" t="n">
+        <v>21</v>
+      </c>
+      <c r="N92" t="n">
+        <v>30</v>
+      </c>
+      <c r="O92" t="n">
+        <v>11</v>
+      </c>
+      <c r="P92" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>5</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1</v>
+      </c>
+      <c r="S92" t="n">
+        <v>25</v>
+      </c>
+      <c r="T92" t="n">
         <v>16</v>
       </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>18</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>1</v>
-      </c>
-      <c r="R92" t="n">
-        <v>5</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>11</v>
-      </c>
       <c r="U92" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V92" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="W92" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="X92" t="n">
         <v>0</v>
@@ -7289,13 +7289,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>45.6</v>
+        <v>239.2</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9806355520872658</v>
+        <v>0.9963311317398624</v>
       </c>
       <c r="D93" t="n">
-        <v>6.918859402848369e-08</v>
+        <v>7.124657327390421e-06</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -7307,13 +7307,13 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -7322,40 +7322,40 @@
         <v>15</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N93" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P93" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T93" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V93" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -7363,73 +7363,73 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>184.8</v>
+        <v>919.6</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>4.600534944508746e-09</v>
+        <v>5.26150065403212e-08</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J94" t="n">
+        <v>32</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>18</v>
+      </c>
+      <c r="M94" t="n">
+        <v>24</v>
+      </c>
+      <c r="N94" t="n">
+        <v>52</v>
+      </c>
+      <c r="O94" t="n">
+        <v>14</v>
+      </c>
+      <c r="P94" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>11</v>
+      </c>
+      <c r="R94" t="n">
+        <v>3</v>
+      </c>
+      <c r="S94" t="n">
+        <v>29</v>
+      </c>
+      <c r="T94" t="n">
+        <v>6</v>
+      </c>
+      <c r="U94" t="n">
+        <v>29</v>
+      </c>
+      <c r="V94" t="n">
         <v>26</v>
       </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
-        <v>15</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="n">
-        <v>42</v>
-      </c>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" t="n">
-        <v>37</v>
-      </c>
-      <c r="S94" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" t="n">
-        <v>29</v>
-      </c>
-      <c r="U94" t="n">
-        <v>0</v>
-      </c>
-      <c r="V94" t="n">
-        <v>34</v>
-      </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="X94" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -7437,13 +7437,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>91.60000000000001</v>
+        <v>311.6</v>
       </c>
       <c r="C95" t="n">
-        <v>0.9998702341886443</v>
+        <v>0.9984037454040966</v>
       </c>
       <c r="D95" t="n">
-        <v>4.30343143472315e-08</v>
+        <v>5.060891196541107e-06</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -7455,55 +7455,55 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
+        <v>6</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>15</v>
+      </c>
+      <c r="M95" t="n">
+        <v>9</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>4</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>13</v>
+      </c>
+      <c r="S95" t="n">
+        <v>15</v>
+      </c>
+      <c r="T95" t="n">
+        <v>12</v>
+      </c>
+      <c r="U95" t="n">
         <v>11</v>
       </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
-        <v>15</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" t="n">
-        <v>11</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>1</v>
-      </c>
-      <c r="R95" t="n">
+      <c r="V95" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" t="n">
         <v>6</v>
       </c>
-      <c r="S95" t="n">
-        <v>0</v>
-      </c>
-      <c r="T95" t="n">
-        <v>15</v>
-      </c>
-      <c r="U95" t="n">
-        <v>0</v>
-      </c>
-      <c r="V95" t="n">
-        <v>15</v>
-      </c>
-      <c r="W95" t="n">
-        <v>0</v>
-      </c>
       <c r="X95" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -7511,13 +7511,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>176.8</v>
+        <v>148</v>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>0.9900406033869418</v>
       </c>
       <c r="D96" t="n">
-        <v>6.752675166154408e-09</v>
+        <v>9.153137089002607e-06</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -7529,55 +7529,55 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N96" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P96" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T96" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V96" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X96" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -7585,73 +7585,73 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>53.6</v>
+        <v>1018</v>
       </c>
       <c r="C97" t="n">
-        <v>0.9970102583526685</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>8.405538465429286e-08</v>
+        <v>1.830155751911465e-08</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J97" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N97" t="n">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P97" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R97" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="T97" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V97" t="n">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -7659,13 +7659,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>118.4</v>
+        <v>166.4</v>
       </c>
       <c r="C98" t="n">
-        <v>0.9997053348317577</v>
+        <v>0.988002551229258</v>
       </c>
       <c r="D98" t="n">
-        <v>1.814270780424305e-08</v>
+        <v>8.547213522745027e-06</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -7677,13 +7677,13 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -7692,34 +7692,34 @@
         <v>15</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N98" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P98" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
+        <v>7</v>
+      </c>
+      <c r="S98" t="n">
         <v>10</v>
       </c>
-      <c r="S98" t="n">
-        <v>0</v>
-      </c>
       <c r="T98" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V98" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="W98" t="n">
         <v>1</v>
@@ -7733,13 +7733,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>46.40000000000001</v>
+        <v>221.6</v>
       </c>
       <c r="C99" t="n">
-        <v>0.9823413437820173</v>
+        <v>0.98898057953595</v>
       </c>
       <c r="D99" t="n">
-        <v>6.832074451889226e-08</v>
+        <v>7.326047629051175e-06</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -7751,13 +7751,13 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -7766,16 +7766,16 @@
         <v>15</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N99" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P99" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -7784,22 +7784,22 @@
         <v>7</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T99" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V99" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -7807,13 +7807,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>84.40000000000001</v>
+        <v>142.8</v>
       </c>
       <c r="C100" t="n">
-        <v>0.9948480311711823</v>
+        <v>0.9921501495573783</v>
       </c>
       <c r="D100" t="n">
-        <v>3.18470202829735e-08</v>
+        <v>9.805119986683717e-06</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -7825,10 +7825,10 @@
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
         <v>1</v>
@@ -7840,40 +7840,40 @@
         <v>15</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N100" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P100" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>7</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T100" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="U100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V100" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W100" t="n">
         <v>1</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101">
@@ -7881,13 +7881,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>48.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="C101" t="n">
-        <v>0.9835067618222262</v>
+        <v>0.9937961124815956</v>
       </c>
       <c r="D101" t="n">
-        <v>6.627280674427369e-08</v>
+        <v>1.199678655958794e-05</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -7899,13 +7899,13 @@
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -7914,34 +7914,34 @@
         <v>15</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N101" t="n">
+        <v>5</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
         <v>9</v>
       </c>
-      <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="n">
-        <v>7</v>
-      </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T101" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W101" t="n">
         <v>0</v>
